--- a/data/trans_dic/P33B_R4-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R4-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 11,9</t>
+          <t>4,21; 13,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 17,87</t>
+          <t>8,89; 19,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 12,66</t>
+          <t>7,52; 14,38</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 12,29</t>
+          <t>5,55; 12,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,29; 16,31</t>
+          <t>10,75; 17,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,93; 13,37</t>
+          <t>8,78; 13,4</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,41; 16,49</t>
+          <t>9,84; 15,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,01; 19,37</t>
+          <t>14,89; 20,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,92; 17,12</t>
+          <t>13,11; 17,0</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 14,66</t>
+          <t>11,15; 16,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,35; 25,06</t>
+          <t>20,3; 25,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,45; 19,02</t>
+          <t>16,59; 20,21</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,59; 19,18</t>
+          <t>13,46; 18,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,9; 32,9</t>
+          <t>27,27; 32,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,92; 25,01</t>
+          <t>21,04; 25,05</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,0; 18,83</t>
+          <t>13,05; 19,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,02; 27,17</t>
+          <t>23,11; 29,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,9; 21,85</t>
+          <t>19,12; 23,45</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,61; 29,69</t>
+          <t>22,23; 30,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,28; 34,81</t>
+          <t>29,27; 35,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,99; 32,13</t>
+          <t>27,57; 32,35</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,85; 14,22</t>
+          <t>12,67; 15,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,93; 22,58</t>
+          <t>21,39; 23,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,43; 18,19</t>
+          <t>17,5; 19,13</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25953</t>
+          <t>31015</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38510</t>
+          <t>49313</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64463</t>
+          <t>80328</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12249; 47600</t>
+          <t>17184; 53151</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23927; 55973</t>
+          <t>32216; 69656</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43650; 90308</t>
+          <t>57907; 110788</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>34752</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>63229</t>
+          <t>67267</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97981</t>
+          <t>107391</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22948; 52062</t>
+          <t>26477; 58207</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37273; 83409</t>
+          <t>53853; 87935</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74121; 124998</t>
+          <t>85910; 131085</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71144</t>
+          <t>77942</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90391</t>
+          <t>107548</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>161536</t>
+          <t>185490</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55632; 88090</t>
+          <t>60925; 96050</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>76011; 105088</t>
+          <t>92643; 125440</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139075; 184350</t>
+          <t>162698; 210963</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>87488</t>
+          <t>95544</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>158837</t>
+          <t>168626</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>246325</t>
+          <t>264170</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37777; 130127</t>
+          <t>78104; 113823</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>130709; 178544</t>
+          <t>149537; 187498</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>151236; 304368</t>
+          <t>238420; 290490</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>91621</t>
+          <t>96945</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>162587</t>
+          <t>182811</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>254208</t>
+          <t>279755</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>76122; 107455</t>
+          <t>81878; 113752</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>146731; 179487</t>
+          <t>165824; 199833</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>231345; 276503</t>
+          <t>255942; 304657</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>58679</t>
+          <t>64881</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>104186</t>
+          <t>114732</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>162864</t>
+          <t>179614</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>47874; 69318</t>
+          <t>53143; 77856</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48764; 165322</t>
+          <t>101499; 128071</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86935; 213375</t>
+          <t>161842; 198433</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>73170</t>
+          <t>81398</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>135215</t>
+          <t>150391</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>208385</t>
+          <t>231789</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>61092; 83961</t>
+          <t>68944; 94407</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>120113; 147852</t>
+          <t>135663; 165145</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>190998; 227324</t>
+          <t>213302; 250269</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>442807</t>
+          <t>487850</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>752955</t>
+          <t>840688</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1195762</t>
+          <t>1328538</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>340557; 491671</t>
+          <t>447367; 536492</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>619270; 825994</t>
+          <t>798390; 882710</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1026657; 1294178</t>
+          <t>1270891; 1389085</t>
         </is>
       </c>
     </row>
